--- a/GBDS AUGUST FILES 2026/SCRR CALCULATOR - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SCRR CALCULATOR - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7042D950-519E-468B-ABDE-5BDE6F440369}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05587293-A9D0-46DD-92EE-64B09244C179}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(AUGUST 2026)" sheetId="814" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <sheet name="(5)" sheetId="2253" r:id="rId14"/>
     <sheet name="08,05 R1" sheetId="2254" r:id="rId15"/>
     <sheet name="08,05 R2" sheetId="2255" r:id="rId16"/>
-    <sheet name="08,05 R3" sheetId="2256" r:id="rId17"/>
+    <sheet name="08,05 R3 NO TRIP" sheetId="2256" r:id="rId17"/>
     <sheet name="(6)" sheetId="2257" r:id="rId18"/>
     <sheet name="08,06 R1" sheetId="2258" r:id="rId19"/>
     <sheet name="08,06 R2" sheetId="2259" r:id="rId20"/>
@@ -67,7 +67,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="12">'08,04 R3'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'08,05 R1'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'08,05 R2'!$A$1:$J$60</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'08,05 R3'!$A$1:$J$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'08,05 R3 NO TRIP'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="18">'08,06 R1'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="19">'08,06 R2'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'08,06 R3'!$A$1:$J$60</definedName>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4306" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4312" uniqueCount="151">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -576,6 +576,18 @@
   </si>
   <si>
     <t>2000008747</t>
+  </si>
+  <si>
+    <t>151284</t>
+  </si>
+  <si>
+    <t>PSBC</t>
+  </si>
+  <si>
+    <t>2130022077</t>
+  </si>
+  <si>
+    <t>153277</t>
   </si>
 </sst>
 </file>
@@ -13445,10 +13457,12 @@
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="10">
+        <v>236</v>
+      </c>
       <c r="D6" s="13">
         <f t="shared" ref="D6:D28" si="1">C6*L6</f>
-        <v>0</v>
+        <v>179596</v>
       </c>
       <c r="F6" s="126" t="s">
         <v>16</v>
@@ -13481,10 +13495,12 @@
       <c r="B7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="10"/>
+      <c r="C7" s="10">
+        <v>15</v>
+      </c>
       <c r="D7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11715</v>
       </c>
       <c r="F7" s="127"/>
       <c r="G7" s="131"/>
@@ -13533,10 +13549,12 @@
       <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="10">
+        <v>113</v>
+      </c>
       <c r="D9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>82829</v>
       </c>
       <c r="F9" s="127"/>
       <c r="G9" s="139"/>
@@ -13651,10 +13669,12 @@
       <c r="B13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="10">
+        <v>8</v>
+      </c>
       <c r="D13" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2456</v>
       </c>
       <c r="F13" s="148" t="s">
         <v>36</v>
@@ -13662,7 +13682,7 @@
       <c r="G13" s="149"/>
       <c r="H13" s="150">
         <f>D29</f>
-        <v>0</v>
+        <v>276596</v>
       </c>
       <c r="I13" s="151"/>
       <c r="J13" s="152"/>
@@ -13696,7 +13716,7 @@
       <c r="G14" s="154"/>
       <c r="H14" s="155">
         <f>D54</f>
-        <v>0</v>
+        <v>37282.5</v>
       </c>
       <c r="I14" s="156"/>
       <c r="J14" s="157"/>
@@ -13734,7 +13754,7 @@
       <c r="G15" s="149"/>
       <c r="H15" s="159">
         <f>H13-H14</f>
-        <v>0</v>
+        <v>239313.5</v>
       </c>
       <c r="I15" s="160"/>
       <c r="J15" s="161"/>
@@ -13773,7 +13793,9 @@
       <c r="G16" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="162"/>
+      <c r="H16" s="162">
+        <v>2034</v>
+      </c>
       <c r="I16" s="162"/>
       <c r="J16" s="162"/>
       <c r="L16" s="6">
@@ -14197,7 +14219,7 @@
       <c r="C29" s="165"/>
       <c r="D29" s="169">
         <f>SUM(D6:D28)</f>
-        <v>0</v>
+        <v>276596</v>
       </c>
       <c r="F29" s="171" t="s">
         <v>54</v>
@@ -14205,7 +14227,7 @@
       <c r="G29" s="172"/>
       <c r="H29" s="175">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27+H28</f>
-        <v>0</v>
+        <v>237279.5</v>
       </c>
       <c r="I29" s="176"/>
       <c r="J29" s="177"/>
@@ -14336,18 +14358,22 @@
       <c r="B34" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="51"/>
+      <c r="C34" s="51">
+        <v>1</v>
+      </c>
       <c r="D34" s="30">
         <f>C34*120</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="40"/>
+      <c r="G34" s="40">
+        <v>11</v>
+      </c>
       <c r="H34" s="203">
         <f t="shared" ref="H34:H39" si="2">F34*G34</f>
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="I34" s="204"/>
       <c r="J34" s="205"/>
@@ -14378,10 +14404,12 @@
       <c r="F35" s="58">
         <v>500</v>
       </c>
-      <c r="G35" s="106"/>
+      <c r="G35" s="106">
+        <v>4</v>
+      </c>
       <c r="H35" s="203">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I35" s="204"/>
       <c r="J35" s="205"/>
@@ -14410,10 +14438,12 @@
       <c r="F36" s="12">
         <v>200</v>
       </c>
-      <c r="G36" s="37"/>
+      <c r="G36" s="37">
+        <v>1</v>
+      </c>
       <c r="H36" s="203">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I36" s="204"/>
       <c r="J36" s="205"/>
@@ -14438,18 +14468,22 @@
       <c r="B37" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="53"/>
+      <c r="C37" s="53">
+        <v>315</v>
+      </c>
       <c r="D37" s="12">
         <f>C37*111</f>
-        <v>0</v>
+        <v>34965</v>
       </c>
       <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="39">
+        <v>9</v>
+      </c>
       <c r="H37" s="203">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I37" s="204"/>
       <c r="J37" s="205"/>
@@ -14472,10 +14506,12 @@
       <c r="B38" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="54"/>
+      <c r="C38" s="54">
+        <v>2</v>
+      </c>
       <c r="D38" s="12">
         <f>C38*84</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="F38" s="30">
         <v>50</v>
@@ -14506,10 +14542,12 @@
       <c r="B39" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="52"/>
+      <c r="C39" s="52">
+        <v>5</v>
+      </c>
       <c r="D39" s="31">
         <f>C39*4.5</f>
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="F39" s="12">
         <v>20</v>
@@ -14540,10 +14578,12 @@
       <c r="B40" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="63"/>
+      <c r="C40" s="63">
+        <v>9</v>
+      </c>
       <c r="D40" s="12">
         <f>C40*111</f>
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="F40" s="12">
         <v>10</v>
@@ -14571,10 +14611,12 @@
       <c r="B41" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="10">
+        <v>1</v>
+      </c>
       <c r="D41" s="12">
         <f>C41*84</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F41" s="12">
         <v>5</v>
@@ -14603,15 +14645,19 @@
       <c r="B42" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="11"/>
+      <c r="C42" s="11">
+        <v>2</v>
+      </c>
       <c r="D42" s="12">
         <f>C42*2.25</f>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F42" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="G42" s="203"/>
+      <c r="G42" s="203">
+        <v>11</v>
+      </c>
       <c r="H42" s="204"/>
       <c r="I42" s="204"/>
       <c r="J42" s="205"/>
@@ -14662,14 +14708,22 @@
       <c r="B44" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="10"/>
+      <c r="C44" s="10">
+        <v>3</v>
+      </c>
       <c r="D44" s="12">
         <f>C44*120</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="37"/>
-      <c r="G44" s="87"/>
-      <c r="H44" s="187"/>
+        <v>360</v>
+      </c>
+      <c r="F44" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="G44" s="62" t="s">
+        <v>147</v>
+      </c>
+      <c r="H44" s="187">
+        <v>223169</v>
+      </c>
       <c r="I44" s="187"/>
       <c r="J44" s="187"/>
       <c r="K44" s="21"/>
@@ -14749,10 +14803,12 @@
       <c r="B48" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="10">
+        <v>5</v>
+      </c>
       <c r="D48" s="12">
         <f>C48*78</f>
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="F48" s="59"/>
       <c r="G48" s="59"/>
@@ -14777,17 +14833,19 @@
       <c r="B49" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="33"/>
+      <c r="C49" s="33">
+        <v>4</v>
+      </c>
       <c r="D49" s="12">
         <f>C49*42</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="F49" s="228" t="s">
         <v>85</v>
       </c>
       <c r="G49" s="175">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46+H47+H48</f>
-        <v>0</v>
+        <v>237280</v>
       </c>
       <c r="H49" s="176"/>
       <c r="I49" s="176"/>
@@ -14811,10 +14869,12 @@
       <c r="B50" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="C50" s="11"/>
+      <c r="C50" s="11">
+        <v>1</v>
+      </c>
       <c r="D50" s="12">
         <f>C50*1.5</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F50" s="229"/>
       <c r="G50" s="178"/>
@@ -14837,11 +14897,11 @@
       <c r="D51" s="31"/>
       <c r="F51" s="230" t="str">
         <f>_xlfn.IFS(H29&gt;G49,"SHORT",H29&lt;G49,"OVER",H29&lt;=G49,"-")</f>
-        <v>-</v>
+        <v>OVER</v>
       </c>
       <c r="G51" s="232">
         <f>G49-H29</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H51" s="233"/>
       <c r="I51" s="233"/>
@@ -14912,7 +14972,7 @@
       <c r="C54" s="217"/>
       <c r="D54" s="220">
         <f>SUM(D34:D53)</f>
-        <v>0</v>
+        <v>37282.5</v>
       </c>
       <c r="F54" s="21"/>
       <c r="J54" s="34"/>
@@ -15228,10 +15288,12 @@
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="10">
+        <v>322</v>
+      </c>
       <c r="D6" s="13">
         <f t="shared" ref="D6:D28" si="1">C6*L6</f>
-        <v>0</v>
+        <v>245042</v>
       </c>
       <c r="F6" s="126" t="s">
         <v>16</v>
@@ -15316,10 +15378,12 @@
       <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="10">
+        <v>21</v>
+      </c>
       <c r="D9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15393</v>
       </c>
       <c r="F9" s="127"/>
       <c r="G9" s="139"/>
@@ -15400,10 +15464,12 @@
       <c r="B12" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="10"/>
+      <c r="C12" s="10">
+        <v>1</v>
+      </c>
       <c r="D12" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="F12" s="145" t="s">
         <v>33</v>
@@ -15434,10 +15500,12 @@
       <c r="B13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="10">
+        <v>10</v>
+      </c>
       <c r="D13" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3070</v>
       </c>
       <c r="F13" s="148" t="s">
         <v>36</v>
@@ -15445,7 +15513,7 @@
       <c r="G13" s="149"/>
       <c r="H13" s="150">
         <f>D29</f>
-        <v>0</v>
+        <v>271026.41666666669</v>
       </c>
       <c r="I13" s="151"/>
       <c r="J13" s="152"/>
@@ -15468,10 +15536,12 @@
       <c r="B14" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="10">
+        <v>10</v>
+      </c>
       <c r="D14" s="31">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>110.41666666666666</v>
       </c>
       <c r="F14" s="153" t="s">
         <v>38</v>
@@ -15479,7 +15549,7 @@
       <c r="G14" s="154"/>
       <c r="H14" s="155">
         <f>D54</f>
-        <v>0</v>
+        <v>36957</v>
       </c>
       <c r="I14" s="156"/>
       <c r="J14" s="157"/>
@@ -15518,7 +15588,7 @@
       <c r="G15" s="149"/>
       <c r="H15" s="159">
         <f>H13-H14</f>
-        <v>0</v>
+        <v>234069.41666666669</v>
       </c>
       <c r="I15" s="160"/>
       <c r="J15" s="161"/>
@@ -15546,10 +15616,12 @@
       <c r="B16" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="10"/>
+      <c r="C16" s="10">
+        <v>2</v>
+      </c>
       <c r="D16" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F16" s="67" t="s">
         <v>41</v>
@@ -15557,7 +15629,9 @@
       <c r="G16" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="162"/>
+      <c r="H16" s="162">
+        <v>1818</v>
+      </c>
       <c r="I16" s="162"/>
       <c r="J16" s="162"/>
       <c r="L16" s="6">
@@ -15618,10 +15692,12 @@
       <c r="B18" s="85" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="10"/>
+      <c r="C18" s="10">
+        <v>1</v>
+      </c>
       <c r="D18" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1102</v>
       </c>
       <c r="F18" s="56"/>
       <c r="G18" s="66" t="s">
@@ -15653,10 +15729,13 @@
       <c r="B19" s="86" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="10">
+        <f>1+1</f>
+        <v>2</v>
+      </c>
       <c r="D19" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2350</v>
       </c>
       <c r="F19" s="56"/>
       <c r="G19" s="68" t="s">
@@ -15710,10 +15789,12 @@
       <c r="B21" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="10">
+        <v>1</v>
+      </c>
       <c r="D21" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1667</v>
       </c>
       <c r="F21" s="69" t="s">
         <v>94</v>
@@ -15980,7 +16061,7 @@
       <c r="C29" s="165"/>
       <c r="D29" s="169">
         <f>SUM(D6:D28)</f>
-        <v>0</v>
+        <v>271026.41666666669</v>
       </c>
       <c r="F29" s="171" t="s">
         <v>54</v>
@@ -15988,7 +16069,7 @@
       <c r="G29" s="172"/>
       <c r="H29" s="175">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27</f>
-        <v>0</v>
+        <v>232251.41666666669</v>
       </c>
       <c r="I29" s="176"/>
       <c r="J29" s="177"/>
@@ -16127,10 +16208,12 @@
       <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="73"/>
+      <c r="G34" s="73">
+        <v>24</v>
+      </c>
       <c r="H34" s="203">
         <f>F34*G34</f>
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="I34" s="204"/>
       <c r="J34" s="205"/>
@@ -16153,18 +16236,22 @@
       <c r="B35" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="52"/>
+      <c r="C35" s="52">
+        <v>1</v>
+      </c>
       <c r="D35" s="30">
         <f>C35*84</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F35" s="58">
         <v>500</v>
       </c>
-      <c r="G35" s="106"/>
+      <c r="G35" s="106">
+        <v>4</v>
+      </c>
       <c r="H35" s="203">
         <f>F35*G35</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I35" s="204"/>
       <c r="J35" s="205"/>
@@ -16185,10 +16272,12 @@
       <c r="B36" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="10"/>
+      <c r="C36" s="10">
+        <v>15</v>
+      </c>
       <c r="D36" s="12">
         <f>C36*1.5</f>
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="F36" s="12">
         <v>200</v>
@@ -16221,18 +16310,22 @@
       <c r="B37" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="53"/>
+      <c r="C37" s="53">
+        <v>316</v>
+      </c>
       <c r="D37" s="12">
         <f>C37*111</f>
-        <v>0</v>
+        <v>35076</v>
       </c>
       <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="39">
+        <v>1</v>
+      </c>
       <c r="H37" s="203">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I37" s="204"/>
       <c r="J37" s="205"/>
@@ -16255,10 +16348,12 @@
       <c r="B38" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="54"/>
+      <c r="C38" s="54">
+        <v>10</v>
+      </c>
       <c r="D38" s="12">
         <f>C38*84</f>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="F38" s="30">
         <v>50</v>
@@ -16289,10 +16384,12 @@
       <c r="B39" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="52"/>
+      <c r="C39" s="52">
+        <v>2</v>
+      </c>
       <c r="D39" s="31">
         <f>C39*4.5</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F39" s="12">
         <v>20</v>
@@ -16323,10 +16420,12 @@
       <c r="B40" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="63"/>
+      <c r="C40" s="63">
+        <v>2</v>
+      </c>
       <c r="D40" s="12">
         <f>C40*111</f>
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="F40" s="12">
         <v>10</v>
@@ -16386,15 +16485,19 @@
       <c r="B42" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="11"/>
+      <c r="C42" s="11">
+        <v>24</v>
+      </c>
       <c r="D42" s="12">
         <f>C42*2.25</f>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F42" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="G42" s="203"/>
+      <c r="G42" s="203">
+        <v>41</v>
+      </c>
       <c r="H42" s="204"/>
       <c r="I42" s="204"/>
       <c r="J42" s="205"/>
@@ -16450,9 +16553,15 @@
         <f>C44*120</f>
         <v>0</v>
       </c>
-      <c r="F44" s="37"/>
-      <c r="G44" s="62"/>
-      <c r="H44" s="187"/>
+      <c r="F44" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="G44" s="87" t="s">
+        <v>149</v>
+      </c>
+      <c r="H44" s="187">
+        <v>70296</v>
+      </c>
       <c r="I44" s="187"/>
       <c r="J44" s="187"/>
       <c r="K44" s="21"/>
@@ -16475,14 +16584,22 @@
       <c r="B45" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C45" s="33"/>
+      <c r="C45" s="33">
+        <v>1</v>
+      </c>
       <c r="D45" s="12">
         <f>C45*84</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="37"/>
-      <c r="G45" s="75"/>
-      <c r="H45" s="187"/>
+        <v>84</v>
+      </c>
+      <c r="F45" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="G45" s="75" t="s">
+        <v>150</v>
+      </c>
+      <c r="H45" s="187">
+        <v>136287</v>
+      </c>
       <c r="I45" s="187"/>
       <c r="J45" s="187"/>
       <c r="K45" s="21"/>
@@ -16495,10 +16612,12 @@
       <c r="B46" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="80"/>
+      <c r="C46" s="80">
+        <v>1</v>
+      </c>
       <c r="D46" s="12">
         <f>C46*1.5</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F46" s="37"/>
       <c r="G46" s="62"/>
@@ -16532,10 +16651,12 @@
       <c r="B48" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="10">
+        <v>4</v>
+      </c>
       <c r="D48" s="12">
         <f>C48*78</f>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="F48" s="59"/>
       <c r="G48" s="59"/>
@@ -16560,17 +16681,19 @@
       <c r="B49" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="33"/>
+      <c r="C49" s="33">
+        <v>6</v>
+      </c>
       <c r="D49" s="12">
         <f>C49*42</f>
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="F49" s="228" t="s">
         <v>85</v>
       </c>
       <c r="G49" s="175">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46+H47+H48</f>
-        <v>0</v>
+        <v>232724</v>
       </c>
       <c r="H49" s="176"/>
       <c r="I49" s="176"/>
@@ -16620,11 +16743,11 @@
       <c r="D51" s="31"/>
       <c r="F51" s="230" t="str">
         <f>_xlfn.IFS(H29&gt;G49,"SHORT",H29&lt;G49,"OVER",H29&lt;=G49,"-")</f>
-        <v>-</v>
+        <v>OVER</v>
       </c>
       <c r="G51" s="232">
         <f>G49-H29</f>
-        <v>0</v>
+        <v>472.58333333331393</v>
       </c>
       <c r="H51" s="233"/>
       <c r="I51" s="233"/>
@@ -16695,7 +16818,7 @@
       <c r="C54" s="217"/>
       <c r="D54" s="220">
         <f>SUM(D34:D53)</f>
-        <v>0</v>
+        <v>36957</v>
       </c>
       <c r="F54" s="21"/>
       <c r="J54" s="34"/>

--- a/GBDS AUGUST FILES 2026/SCRR CALCULATOR - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SCRR CALCULATOR - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60366DD9-D59E-40E8-A025-998B891A95D9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59C1841-49B4-41EE-B412-4601710E23B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="19" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(AUGUST 2026)" sheetId="814" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <sheet name="08,07 R2" sheetId="2263" r:id="rId24"/>
     <sheet name="08,07 R3" sheetId="2264" r:id="rId25"/>
     <sheet name="(8)" sheetId="2265" r:id="rId26"/>
-    <sheet name="08,08 R1" sheetId="2266" r:id="rId27"/>
+    <sheet name="08,08 R1 NO TRIP" sheetId="2266" r:id="rId27"/>
     <sheet name="08,08 R2" sheetId="2267" r:id="rId28"/>
     <sheet name="08,08 R3" sheetId="2268" r:id="rId29"/>
     <sheet name="(10)" sheetId="2269" r:id="rId30"/>
@@ -74,7 +74,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="22">'08,07 R1'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="23">'08,07 R2'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="24">'08,07 R3'!$A$1:$J$60</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="26">'08,08 R1'!$A$1:$J$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="26">'08,08 R1 NO TRIP'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="27">'08,08 R2'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'08,08 R3'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="30">'08,10 R1'!$A$1:$J$60</definedName>
@@ -204,7 +204,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4329" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4332" uniqueCount="159">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -681,6 +681,9 @@
   </si>
   <si>
     <t>2000008766</t>
+  </si>
+  <si>
+    <t>2000003304</t>
   </si>
 </sst>
 </file>
@@ -38079,10 +38082,12 @@
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="10">
+        <v>273</v>
+      </c>
       <c r="D6" s="13">
         <f t="shared" ref="D6:D28" si="1">C6*L6</f>
-        <v>0</v>
+        <v>207753</v>
       </c>
       <c r="F6" s="216" t="s">
         <v>16</v>
@@ -38115,10 +38120,12 @@
       <c r="B7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="10"/>
+      <c r="C7" s="10">
+        <v>9</v>
+      </c>
       <c r="D7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7029</v>
       </c>
       <c r="F7" s="217"/>
       <c r="G7" s="221"/>
@@ -38167,10 +38174,12 @@
       <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="10">
+        <v>12</v>
+      </c>
       <c r="D9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8796</v>
       </c>
       <c r="F9" s="217"/>
       <c r="G9" s="228"/>
@@ -38285,10 +38294,12 @@
       <c r="B13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="10">
+        <v>11</v>
+      </c>
       <c r="D13" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3377</v>
       </c>
       <c r="F13" s="237" t="s">
         <v>36</v>
@@ -38296,7 +38307,7 @@
       <c r="G13" s="201"/>
       <c r="H13" s="192">
         <f>D29</f>
-        <v>0</v>
+        <v>226955</v>
       </c>
       <c r="I13" s="193"/>
       <c r="J13" s="194"/>
@@ -38330,7 +38341,7 @@
       <c r="G14" s="196"/>
       <c r="H14" s="197">
         <f>D54</f>
-        <v>0</v>
+        <v>33465.75</v>
       </c>
       <c r="I14" s="198"/>
       <c r="J14" s="199"/>
@@ -38369,7 +38380,7 @@
       <c r="G15" s="201"/>
       <c r="H15" s="202">
         <f>H13-H14</f>
-        <v>0</v>
+        <v>193489.25</v>
       </c>
       <c r="I15" s="203"/>
       <c r="J15" s="204"/>
@@ -38408,7 +38419,9 @@
       <c r="G16" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="162"/>
+      <c r="H16" s="162">
+        <v>1350</v>
+      </c>
       <c r="I16" s="162"/>
       <c r="J16" s="162"/>
       <c r="L16" s="6">
@@ -38736,9 +38749,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F26" s="64"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="183"/>
+      <c r="F26" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="G26" s="59">
+        <v>11720</v>
+      </c>
+      <c r="H26" s="183">
+        <v>67927</v>
+      </c>
       <c r="I26" s="184"/>
       <c r="J26" s="185"/>
       <c r="L26" s="7">
@@ -38831,7 +38850,7 @@
       <c r="C29" s="165"/>
       <c r="D29" s="169">
         <f>SUM(D6:D28)</f>
-        <v>0</v>
+        <v>226955</v>
       </c>
       <c r="F29" s="109" t="s">
         <v>54</v>
@@ -38839,7 +38858,7 @@
       <c r="G29" s="171"/>
       <c r="H29" s="131">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27</f>
-        <v>0</v>
+        <v>260066.25</v>
       </c>
       <c r="I29" s="132"/>
       <c r="J29" s="133"/>
@@ -38978,10 +38997,12 @@
       <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="73"/>
+      <c r="G34" s="73">
+        <v>100</v>
+      </c>
       <c r="H34" s="153">
         <f>F34*G34</f>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="I34" s="154"/>
       <c r="J34" s="155"/>
@@ -39012,10 +39033,12 @@
       <c r="F35" s="58">
         <v>500</v>
       </c>
-      <c r="G35" s="106"/>
+      <c r="G35" s="106">
+        <v>319</v>
+      </c>
       <c r="H35" s="153">
         <f>F35*G35</f>
-        <v>0</v>
+        <v>159500</v>
       </c>
       <c r="I35" s="154"/>
       <c r="J35" s="155"/>
@@ -39072,18 +39095,22 @@
       <c r="B37" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="53"/>
+      <c r="C37" s="53">
+        <v>293</v>
+      </c>
       <c r="D37" s="12">
         <f>C37*111</f>
-        <v>0</v>
+        <v>32523</v>
       </c>
       <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="39">
+        <v>4</v>
+      </c>
       <c r="H37" s="153">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I37" s="154"/>
       <c r="J37" s="155"/>
@@ -39106,10 +39133,12 @@
       <c r="B38" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="54"/>
+      <c r="C38" s="54">
+        <v>1</v>
+      </c>
       <c r="D38" s="12">
         <f>C38*84</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F38" s="30">
         <v>50</v>
@@ -39140,10 +39169,12 @@
       <c r="B39" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="52"/>
+      <c r="C39" s="52">
+        <v>4</v>
+      </c>
       <c r="D39" s="31">
         <f>C39*4.5</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F39" s="12">
         <v>20</v>
@@ -39205,10 +39236,12 @@
       <c r="B41" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="10">
+        <v>1</v>
+      </c>
       <c r="D41" s="12">
         <f>C41*84</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F41" s="12">
         <v>5</v>
@@ -39237,15 +39270,19 @@
       <c r="B42" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="11"/>
+      <c r="C42" s="11">
+        <v>3</v>
+      </c>
       <c r="D42" s="12">
         <f>C42*2.25</f>
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="F42" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="G42" s="153"/>
+      <c r="G42" s="153">
+        <v>52</v>
+      </c>
       <c r="H42" s="154"/>
       <c r="I42" s="154"/>
       <c r="J42" s="155"/>
@@ -39296,10 +39333,12 @@
       <c r="B44" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="10"/>
+      <c r="C44" s="10">
+        <v>1</v>
+      </c>
       <c r="D44" s="12">
         <f>C44*120</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F44" s="37"/>
       <c r="G44" s="62"/>
@@ -39383,10 +39422,12 @@
       <c r="B48" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="10">
+        <v>1</v>
+      </c>
       <c r="D48" s="12">
         <f>C48*78</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F48" s="59"/>
       <c r="G48" s="59"/>
@@ -39411,17 +39452,19 @@
       <c r="B49" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="33"/>
+      <c r="C49" s="33">
+        <v>13</v>
+      </c>
       <c r="D49" s="12">
         <f>C49*42</f>
-        <v>0</v>
+        <v>546</v>
       </c>
       <c r="F49" s="129" t="s">
         <v>85</v>
       </c>
       <c r="G49" s="131">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46+H47+H48</f>
-        <v>0</v>
+        <v>259952</v>
       </c>
       <c r="H49" s="132"/>
       <c r="I49" s="132"/>
@@ -39445,10 +39488,12 @@
       <c r="B50" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="C50" s="80"/>
+      <c r="C50" s="80">
+        <v>4</v>
+      </c>
       <c r="D50" s="12">
         <f>C50*1.5</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F50" s="130"/>
       <c r="G50" s="134"/>
@@ -39471,11 +39516,11 @@
       <c r="D51" s="31"/>
       <c r="F51" s="137" t="str">
         <f>_xlfn.IFS(H29&gt;G49,"SHORT",H29&lt;G49,"OVER",H29&lt;=G49,"-")</f>
-        <v>-</v>
+        <v>SHORT</v>
       </c>
       <c r="G51" s="139">
         <f>G49-H29</f>
-        <v>0</v>
+        <v>-114.25</v>
       </c>
       <c r="H51" s="140"/>
       <c r="I51" s="140"/>
@@ -39546,7 +39591,7 @@
       <c r="C54" s="111"/>
       <c r="D54" s="115">
         <f>SUM(D34:D53)</f>
-        <v>0</v>
+        <v>33465.75</v>
       </c>
       <c r="F54" s="21"/>
       <c r="J54" s="34"/>
@@ -39837,10 +39882,12 @@
       <c r="B6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="10">
+        <v>280</v>
+      </c>
       <c r="D6" s="13">
         <f t="shared" ref="D6:D28" si="1">C6*L6</f>
-        <v>0</v>
+        <v>213080</v>
       </c>
       <c r="F6" s="216" t="s">
         <v>16</v>
@@ -39873,10 +39920,12 @@
       <c r="B7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="10"/>
+      <c r="C7" s="10">
+        <v>6</v>
+      </c>
       <c r="D7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4686</v>
       </c>
       <c r="F7" s="217"/>
       <c r="G7" s="221"/>
@@ -39925,10 +39974,12 @@
       <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="10">
+        <v>108</v>
+      </c>
       <c r="D9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>79164</v>
       </c>
       <c r="F9" s="217"/>
       <c r="G9" s="228"/>
@@ -39949,10 +40000,12 @@
       <c r="B10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="10"/>
+      <c r="C10" s="10">
+        <v>2</v>
+      </c>
       <c r="D10" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2064</v>
       </c>
       <c r="F10" s="216" t="s">
         <v>26</v>
@@ -40009,10 +40062,12 @@
       <c r="B12" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="10"/>
+      <c r="C12" s="10">
+        <v>2</v>
+      </c>
       <c r="D12" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1984</v>
       </c>
       <c r="F12" s="234" t="s">
         <v>33</v>
@@ -40043,10 +40098,12 @@
       <c r="B13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="10">
+        <v>7</v>
+      </c>
       <c r="D13" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2149</v>
       </c>
       <c r="F13" s="237" t="s">
         <v>36</v>
@@ -40054,7 +40111,7 @@
       <c r="G13" s="201"/>
       <c r="H13" s="192">
         <f>D29</f>
-        <v>0</v>
+        <v>303138.04166666669</v>
       </c>
       <c r="I13" s="193"/>
       <c r="J13" s="194"/>
@@ -40077,10 +40134,12 @@
       <c r="B14" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="10">
+        <v>1</v>
+      </c>
       <c r="D14" s="31">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11.041666666666666</v>
       </c>
       <c r="F14" s="195" t="s">
         <v>38</v>
@@ -40088,7 +40147,7 @@
       <c r="G14" s="196"/>
       <c r="H14" s="197">
         <f>D54</f>
-        <v>0</v>
+        <v>26834.25</v>
       </c>
       <c r="I14" s="198"/>
       <c r="J14" s="199"/>
@@ -40126,7 +40185,7 @@
       <c r="G15" s="201"/>
       <c r="H15" s="202">
         <f>H13-H14</f>
-        <v>0</v>
+        <v>276303.79166666669</v>
       </c>
       <c r="I15" s="203"/>
       <c r="J15" s="204"/>
@@ -40165,7 +40224,9 @@
       <c r="G16" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="162"/>
+      <c r="H16" s="162">
+        <v>1944</v>
+      </c>
       <c r="I16" s="162"/>
       <c r="J16" s="162"/>
       <c r="L16" s="6">
@@ -40589,7 +40650,7 @@
       <c r="C29" s="165"/>
       <c r="D29" s="169">
         <f>SUM(D6:D28)</f>
-        <v>0</v>
+        <v>303138.04166666669</v>
       </c>
       <c r="F29" s="109" t="s">
         <v>54</v>
@@ -40597,7 +40658,7 @@
       <c r="G29" s="171"/>
       <c r="H29" s="131">
         <f>H15-H16-H17-H18-H19-H20-H22-H23-H24+H26+H27</f>
-        <v>0</v>
+        <v>274359.79166666669</v>
       </c>
       <c r="I29" s="132"/>
       <c r="J29" s="133"/>
@@ -40728,18 +40789,22 @@
       <c r="B34" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="51"/>
+      <c r="C34" s="51">
+        <v>1</v>
+      </c>
       <c r="D34" s="30">
         <f>C34*120</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F34" s="12">
         <v>1000</v>
       </c>
-      <c r="G34" s="73"/>
+      <c r="G34" s="73">
+        <v>37</v>
+      </c>
       <c r="H34" s="153">
         <f>F34*G34</f>
-        <v>0</v>
+        <v>37000</v>
       </c>
       <c r="I34" s="154"/>
       <c r="J34" s="155"/>
@@ -40762,18 +40827,22 @@
       <c r="B35" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="52"/>
+      <c r="C35" s="52">
+        <v>1</v>
+      </c>
       <c r="D35" s="30">
         <f>C35*84</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F35" s="58">
         <v>500</v>
       </c>
-      <c r="G35" s="106"/>
+      <c r="G35" s="106">
+        <v>25</v>
+      </c>
       <c r="H35" s="153">
         <f>F35*G35</f>
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="I35" s="154"/>
       <c r="J35" s="155"/>
@@ -40794,10 +40863,12 @@
       <c r="B36" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="10"/>
+      <c r="C36" s="10">
+        <v>20</v>
+      </c>
       <c r="D36" s="12">
         <f>C36*1.5</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F36" s="12">
         <v>200</v>
@@ -40830,18 +40901,22 @@
       <c r="B37" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="53"/>
+      <c r="C37" s="53">
+        <v>224</v>
+      </c>
       <c r="D37" s="12">
         <f>C37*111</f>
-        <v>0</v>
+        <v>24864</v>
       </c>
       <c r="F37" s="12">
         <v>100</v>
       </c>
-      <c r="G37" s="39"/>
+      <c r="G37" s="39">
+        <v>6</v>
+      </c>
       <c r="H37" s="153">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I37" s="154"/>
       <c r="J37" s="155"/>
@@ -40864,18 +40939,22 @@
       <c r="B38" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="54"/>
+      <c r="C38" s="54">
+        <v>7</v>
+      </c>
       <c r="D38" s="12">
         <f>C38*84</f>
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="F38" s="30">
         <v>50</v>
       </c>
-      <c r="G38" s="39"/>
+      <c r="G38" s="39">
+        <v>1</v>
+      </c>
       <c r="H38" s="153">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I38" s="154"/>
       <c r="J38" s="155"/>
@@ -40932,10 +41011,12 @@
       <c r="B40" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="63"/>
+      <c r="C40" s="63">
+        <v>4</v>
+      </c>
       <c r="D40" s="12">
         <f>C40*111</f>
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="F40" s="12">
         <v>10</v>
@@ -40963,10 +41044,12 @@
       <c r="B41" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="10">
+        <v>2</v>
+      </c>
       <c r="D41" s="12">
         <f>C41*84</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="F41" s="12">
         <v>5</v>
@@ -40995,15 +41078,19 @@
       <c r="B42" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="11"/>
+      <c r="C42" s="11">
+        <v>1</v>
+      </c>
       <c r="D42" s="12">
         <f>C42*2.25</f>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="F42" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="G42" s="153"/>
+      <c r="G42" s="153">
+        <v>15</v>
+      </c>
       <c r="H42" s="154"/>
       <c r="I42" s="154"/>
       <c r="J42" s="155"/>
@@ -41054,14 +41141,22 @@
       <c r="B44" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="10"/>
+      <c r="C44" s="10">
+        <v>1</v>
+      </c>
       <c r="D44" s="12">
         <f>C44*120</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="37"/>
-      <c r="G44" s="62"/>
-      <c r="H44" s="148"/>
+        <v>120</v>
+      </c>
+      <c r="F44" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="G44" s="87" t="s">
+        <v>158</v>
+      </c>
+      <c r="H44" s="148">
+        <v>224164</v>
+      </c>
       <c r="I44" s="148"/>
       <c r="J44" s="148"/>
       <c r="K44" s="21"/>
@@ -41084,10 +41179,12 @@
       <c r="B45" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C45" s="33"/>
+      <c r="C45" s="33">
+        <v>1</v>
+      </c>
       <c r="D45" s="12">
         <f>C45*84</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F45" s="37"/>
       <c r="G45" s="62"/>
@@ -41104,10 +41201,12 @@
       <c r="B46" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="80"/>
+      <c r="C46" s="80">
+        <v>1</v>
+      </c>
       <c r="D46" s="12">
         <f>C46*1.5</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F46" s="37"/>
       <c r="G46" s="75"/>
@@ -41141,10 +41240,12 @@
       <c r="B48" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="10">
+        <v>2</v>
+      </c>
       <c r="D48" s="12">
         <f>C48*78</f>
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="F48" s="59"/>
       <c r="G48" s="59"/>
@@ -41169,17 +41270,19 @@
       <c r="B49" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="33"/>
+      <c r="C49" s="33">
+        <v>4</v>
+      </c>
       <c r="D49" s="12">
         <f>C49*42</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="F49" s="129" t="s">
         <v>85</v>
       </c>
       <c r="G49" s="131">
         <f>H34+H35+H36+H37+H38+H39+H40+H41+G42+H44+H45+H46+H47+H48</f>
-        <v>0</v>
+        <v>274329</v>
       </c>
       <c r="H49" s="132"/>
       <c r="I49" s="132"/>
@@ -41203,10 +41306,12 @@
       <c r="B50" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="C50" s="11"/>
+      <c r="C50" s="11">
+        <v>3</v>
+      </c>
       <c r="D50" s="12">
         <f>C50*1.5</f>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F50" s="130"/>
       <c r="G50" s="134"/>
@@ -41229,11 +41334,11 @@
       <c r="D51" s="31"/>
       <c r="F51" s="137" t="str">
         <f>_xlfn.IFS(H29&gt;G49,"SHORT",H29&lt;G49,"OVER",H29&lt;=G49,"-")</f>
-        <v>-</v>
+        <v>SHORT</v>
       </c>
       <c r="G51" s="139">
         <f>G49-H29</f>
-        <v>0</v>
+        <v>-30.791666666686069</v>
       </c>
       <c r="H51" s="140"/>
       <c r="I51" s="140"/>
@@ -41304,7 +41409,7 @@
       <c r="C54" s="111"/>
       <c r="D54" s="115">
         <f>SUM(D34:D53)</f>
-        <v>0</v>
+        <v>26834.25</v>
       </c>
       <c r="F54" s="21"/>
       <c r="J54" s="34"/>
